--- a/estudiantes.xlsx
+++ b/estudiantes.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E56"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,19 +418,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Angel</v>
+        <v>Alessia</v>
       </c>
       <c r="B2" t="str">
-        <v>Estudio de Czerny(pág 38), Etude Débutants</v>
+        <v>Pas Vite</v>
       </c>
       <c r="C2" t="str">
-        <v>Simultaneidad</v>
+        <v>Uso de Brazo y Legato</v>
       </c>
       <c r="D2" t="str">
-        <v>1-4</v>
+        <v>1-8</v>
       </c>
       <c r="E2" t="str">
-        <v>Terminó  y repasó la pieza, debe  tener cuidado con el ritmo, el final y tratar de conseguir una buena articulación y fluidez.</v>
+        <v xml:space="preserve">Ejecutó muy bien el Legato de 3 notas, haciendo buen uso del brazo., Tocó la pieza acompañada de su profesor. </v>
       </c>
     </row>
     <row r="3">
@@ -438,33 +438,33 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v>El Preso, Wanyoma</v>
+        <v xml:space="preserve">Danza en C Mayor - Cornelius Gurlitt </v>
       </c>
       <c r="C3" t="str">
         <v>Simultaneidad</v>
       </c>
       <c r="D3" t="str">
-        <v>1-12</v>
+        <v>1-4</v>
       </c>
       <c r="E3" t="str">
-        <v>Practicamos en clase la introducción. El eligió su propia digitación. Estamos empezando segunda parte, practicamos con manos separadas.</v>
+        <v>Seguimos trabajando primer sistema con dos manos. Esta haciendo buen uso del 3er(Aunque este le cuesta un poco más) y 5to dedo en la mano izquierda.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Esther</v>
+        <v>Angel</v>
       </c>
       <c r="B4" t="str">
-        <v>Bavardage, Etude Debuntants</v>
+        <v>Gotta Get Up, Harry Nilson</v>
       </c>
       <c r="C4" t="str">
-        <v xml:space="preserve">Simultaneidad - Escala </v>
+        <v>Simultaneidad</v>
       </c>
       <c r="D4" t="str">
         <v>1-8</v>
       </c>
       <c r="E4" t="str">
-        <v>Repasamos en clase y pudo ejecutar el primer sistema con relativa fluidez, hay que estar muy pendiente si realmente está repasando. Debe estudiar mas en casa., Debemos empezar ahora segundo sistema.</v>
+        <v xml:space="preserve">NO VINO, Repasamos la primera parte de la pieza, tenía tiempo sin venir., Mejoró mucho la anticipación y ejecución en el compás 11 con el acorde de la mano derecha, debe tener mucho cuidado con la digitación y no correr., Llegamos a la parte donde se alternan las manos, lo estoy acompañando con la voz., Repasamos la ejecución de los acordes de ambas manos en el primer sistema y el uso de las octavas. , , </v>
       </c>
     </row>
     <row r="5">
@@ -472,50 +472,38 @@
         <v/>
       </c>
       <c r="B5" t="str">
-        <v>Cuán Lejos Voy - Lil Manuel Miranda</v>
-      </c>
-      <c r="C5" t="str">
-        <v xml:space="preserve">Simultaneidad </v>
-      </c>
-      <c r="D5" t="str">
-        <v>1-7</v>
+        <v>Queen</v>
       </c>
       <c r="E5" t="str">
-        <v xml:space="preserve">Repasamos el tema principal de la obra, y repasamos segunda parte con manos separadas, pero debe repasar más para tener fluidez. Debe tener cuidado con el figuraje del tema principal y los cambios en la armonía. </v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Isabella_Garcia</v>
+        <v/>
       </c>
       <c r="B6" t="str">
-        <v>Pequeños Compañeros de Juego - Franz Chwatal</v>
-      </c>
-      <c r="C6" t="str">
-        <v xml:space="preserve">Simultaneidad </v>
-      </c>
-      <c r="D6" t="str">
-        <v>1-8</v>
+        <v>De los pequeños cisnes</v>
       </c>
       <c r="E6" t="str">
-        <v>NO VINO, Terminó los dos sistemas. Debe seguir repasando y tener cuidado con la izquierda durante el cambio de acorde con el quinto dedo.</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
+        <v>Esther</v>
       </c>
       <c r="B7" t="str">
-        <v xml:space="preserve">Alouette - Canción Folclórica Francesa </v>
+        <v>Sonatina de Clementi</v>
       </c>
       <c r="C7" t="str">
-        <v xml:space="preserve">Simultaneidad </v>
+        <v xml:space="preserve">Simultaneidad - Escala </v>
       </c>
       <c r="D7" t="str">
-        <v>1-4</v>
+        <v>1-8</v>
       </c>
       <c r="E7" t="str">
-        <v>Debemos seguir repasando con las dos manos. Ejecuto bien la primera parte. Buena utilización del quinto.  Ya ejecutó el segundo sistema que es en su mayoría una monodia.</v>
+        <v xml:space="preserve">Terminando el tercer sistema, está trabajando bien relación 5to-Pulgar con mas confianza. Y ha trabajado bien la dificultad de la polifonía., , , </v>
       </c>
     </row>
     <row r="8">
@@ -523,35 +511,41 @@
         <v/>
       </c>
       <c r="B8" t="str">
-        <v xml:space="preserve">Sing Bird sing - Bastien </v>
+        <v>Cuán Lejos Voy - Lil Manuel Miranda</v>
+      </c>
+      <c r="C8" t="str">
+        <v xml:space="preserve">Simultaneidad </v>
+      </c>
+      <c r="D8" t="str">
+        <v>1-7</v>
       </c>
       <c r="E8" t="str">
-        <v>Empezó con mano izquierda, vamos a hacer este estudio para que gane más confianza con los acordes.</v>
+        <v xml:space="preserve">Terminó la pieza pero debe tener cuidado con el figuraje del tema principal y los cambios en la armonía, sobre todo al final. </v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Isabella_Rincon</v>
+        <v/>
       </c>
       <c r="B9" t="str">
-        <v>Himno de La Alegría - Beethoven</v>
+        <v>Corazon Valiente - James Horner</v>
       </c>
       <c r="C9" t="str">
         <v>Simultaneidad</v>
       </c>
       <c r="D9" t="str">
-        <v>1-4</v>
+        <v>1-8</v>
       </c>
       <c r="E9" t="str">
-        <v>Terminó la pieza. Debe estar pendiente del cambio en el final. Pero debe repasar más. Tiene que articular mejor los dedos.  En la izquierda hizo una voz descendente que ella misma improvisó con éxito, mostró interés por esta pieza.</v>
+        <v>Trabajamos hasta segundo sistema lentamente, ha entendido muy bien el motivo principal.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v/>
+        <v>Isabella_Garcia</v>
       </c>
       <c r="B10" t="str">
-        <v>Fiesta de Cumpleaños - Thompson</v>
+        <v xml:space="preserve">Sing Bird sing - Bastien </v>
       </c>
       <c r="C10" t="str">
         <v>Simultaneidad</v>
@@ -560,41 +554,41 @@
         <v>1-4</v>
       </c>
       <c r="E10" t="str">
-        <v>Ejecutó toda la monodia,  mejoró mucho el uso de la izquierda, hizo mucho mejor la relación 5to - pulgar.</v>
+        <v>Ejecutó bien la segunda parte de la pieza, que es un poco mas sencilla. Esta haciendo muy bien la simultaneidad, y correcto uso de 5to dedo.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Jeronimo</v>
+        <v/>
       </c>
       <c r="B11" t="str">
-        <v>Everybody wants to Rule the World - Tears for Fears</v>
+        <v>Aura lee</v>
       </c>
       <c r="C11" t="str">
-        <v>Simultaneidad</v>
+        <v xml:space="preserve">Simultaneidad </v>
       </c>
       <c r="D11" t="str">
         <v>1-4</v>
       </c>
       <c r="E11" t="str">
-        <v xml:space="preserve">NO VINO, Repasó las dos primeras partes de la pieza, con la variación en la segunda parte que pudimos repasar satisfactoriamente. Debe seguir estudiando. Siempre cuidando digitación., </v>
+        <v>Ejecutó bien el motivo principal con dos manos. Debe repasar para empezar el segundo sistema.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>Isabella_Rincon</v>
       </c>
       <c r="B12" t="str">
-        <v xml:space="preserve">Minuet in C, Op 1 - Alexander Reinagle </v>
+        <v>Mercado Persa</v>
       </c>
       <c r="C12" t="str">
         <v>Simultaneidad</v>
       </c>
       <c r="D12" t="str">
-        <v>1-4</v>
+        <v>1-8</v>
       </c>
       <c r="E12" t="str">
-        <v>Repaso en clases los primeros compases a dos manos. Debe practicar más. Me informa que casi no tiene tiempo de estudiar en casa.</v>
+        <v>Estudiamos  los dos primeros sistemas(Solo Mano Derecha). Haciendo énfasis en el uso de tercer y cuarto dedo(que se le dificulta un poco). Le causa gran estres tocar con la izquierda.</v>
       </c>
     </row>
     <row r="13">
@@ -602,7 +596,7 @@
         <v/>
       </c>
       <c r="B13" t="str">
-        <v>Yo te extrañaré - Canción del tercer Cielo</v>
+        <v xml:space="preserve">Danza en C Mayor - Cornelius Gurlitt </v>
       </c>
       <c r="C13" t="str">
         <v>Simultaneidad</v>
@@ -611,32 +605,26 @@
         <v>1-4</v>
       </c>
       <c r="E13" t="str">
-        <v>Trabajamos armonía, pudo ejecutar los 3 primeros acordes con la mano izquierda.  Hicimos primer sistema, en la segunda armonía solo hicimos intervalos debido  a la dificultad para hacer acordes.</v>
+        <v>Está estudiando legato de 5 notas en la mano derecha. Trabajó un poco mano izquierda.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Juan_Camilo</v>
+        <v/>
       </c>
       <c r="B14" t="str">
-        <v>Comedy - Hoshino Gen</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Simultaneidad</v>
-      </c>
-      <c r="D14" t="str">
-        <v>1-4</v>
+        <v>Another Love</v>
       </c>
       <c r="E14" t="str">
-        <v xml:space="preserve">Muestra gran conexión con el ritmo de la pieza. En la última parte debe ser más preciso con la digitación. , Hay que estar pendiente que no descanse la muñeca en el teclado., , </v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v/>
+        <v>Jeronimo</v>
       </c>
       <c r="B15" t="str">
-        <v>Jurassic Park - John Williams</v>
+        <v>Everybody wants to Rule the World - Tears for Fears</v>
       </c>
       <c r="C15" t="str">
         <v>Simultaneidad</v>
@@ -645,7 +633,7 @@
         <v>1-4</v>
       </c>
       <c r="E15" t="str">
-        <v>Ya terminó la pieza, debe tener cuidado con los cambios en la izquierda, sobre todo al final, se siente muy conectado con el ritmo.</v>
+        <v xml:space="preserve">NO VINO, Repasó las dos primeras partes de la pieza, con la variación en la segunda parte que pudimos repasar satisfactoriamente. Debe seguir estudiando. Siempre cuidando digitación., </v>
       </c>
     </row>
     <row r="16">
@@ -653,33 +641,33 @@
         <v/>
       </c>
       <c r="B16" t="str">
-        <v>Toccata en D menor</v>
+        <v>Yo te extrañaré - Canción del tercer Cielo</v>
       </c>
       <c r="C16" t="str">
         <v>Simultaneidad</v>
       </c>
       <c r="D16" t="str">
-        <v>1-8</v>
+        <v>1-4</v>
       </c>
       <c r="E16" t="str">
-        <v>Estudiamos buen uso de la digitación y adornos.</v>
+        <v>Trabajamos armonía, pudo ejecutar los 3 primeros acordes(en realidad intervalos) con la mano izquierda.  Ejecutó toda la pieza, pero debe practicar mucho.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Juan_Pablo</v>
+        <v>Juan_Camilo</v>
       </c>
       <c r="B17" t="str">
-        <v>20. Avec Doceur - Etude Debutants</v>
+        <v>Beethoven 5</v>
       </c>
       <c r="C17" t="str">
-        <v>Legato - Brazo</v>
+        <v>Simultaneidad - Dinámicas</v>
       </c>
       <c r="D17" t="str">
-        <v>1-4</v>
+        <v>1-32</v>
       </c>
       <c r="E17" t="str">
-        <v>NO VINO, Trabajó Legato en ambas manos. Le falta practicar más el final, y escucharla en su totalidad.</v>
+        <v xml:space="preserve">NO VA A VENIR HASTA EL 24, Terminamos la pieza, es necesario seguir trabajando la pieza concentrados en el tempo y cuidando la digitación., Continuamos trabajando haciendo énfasis en los acentos que debe hacer para no perder el ritmo de la pieza., Trabajó bastante bien a dos manos, hicimos énfasis en el tempo., , </v>
       </c>
     </row>
     <row r="18">
@@ -687,33 +675,27 @@
         <v/>
       </c>
       <c r="B18" t="str">
-        <v>Fiesta de Cumpleaños, Thompson</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Legato - Brazo</v>
-      </c>
-      <c r="D18" t="str">
-        <v>1-4</v>
+        <v>Cuatro Estaciones de Vivaldi</v>
       </c>
       <c r="E18" t="str">
-        <v xml:space="preserve">Trabajamos legato en ambos brazos. </v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lorena</v>
+        <v/>
       </c>
       <c r="B19" t="str">
-        <v>Swan Lake Waltz - Tchaikovsky</v>
+        <v xml:space="preserve">Titanic </v>
       </c>
       <c r="C19" t="str">
-        <v xml:space="preserve">Simultaneidad </v>
+        <v>Simultaneidad</v>
       </c>
       <c r="D19" t="str">
-        <v>1-16</v>
+        <v>1-8</v>
       </c>
       <c r="E19" t="str">
-        <v xml:space="preserve">NO VINO, Está tocando bastante bien, los saltos de la izquierda los hace de manera fluida. Seguimos con la introducción, que es una especie de escala. , Ya terminó el Vals. </v>
+        <v xml:space="preserve">Trabajamos los dos primeros sistema. Es necesario trabajar más con los acordes. </v>
       </c>
     </row>
     <row r="20">
@@ -721,64 +703,67 @@
         <v/>
       </c>
       <c r="B20" t="str">
-        <v>Aura Lee - George Poulton</v>
+        <v>Jurassic Park</v>
       </c>
       <c r="C20" t="str">
-        <v>Simultaneidad</v>
+        <v>Simultaniedad</v>
       </c>
       <c r="D20" t="str">
-        <v>1-16</v>
+        <v>1-12</v>
       </c>
       <c r="E20" t="str">
-        <v xml:space="preserve">Repasamos a 4 manos la primera página de manera satisfactoria. , </v>
+        <v>Terminó la pieza. Debe seguir repasando.</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v/>
+        <v>Juan_Pablo</v>
       </c>
       <c r="B21" t="str">
-        <v>Thousand Years - A Thousand Years</v>
+        <v>20. Avec Doceur - Etude Debutants</v>
       </c>
       <c r="C21" t="str">
-        <v>Simultaneidad - Christina Perri</v>
+        <v>Legato - Brazo</v>
+      </c>
+      <c r="D21" t="str">
+        <v>1-8</v>
       </c>
       <c r="E21" t="str">
-        <v>Ejecutó bien la primera página, resolvió bien el pivoteo con mano izquierda en la segunda página.</v>
+        <v>Debe anticipar las manos y no bajarlas tanto., , Trabajó Legato en ambas manos. La ejecutó toda pero le falta practicar más el final, y escucharla en su totalidad.</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Lorenzo</v>
+        <v/>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">Tambores Indios </v>
+        <v>Fiesta de Cumpleaños, Thompson</v>
       </c>
       <c r="C22" t="str">
-        <v xml:space="preserve">Simultaneidad </v>
+        <v>Legato - Brazo</v>
       </c>
       <c r="D22" t="str">
-        <v>1-8</v>
+        <v>1-4</v>
       </c>
       <c r="E22" t="str">
-        <v>Ya ejecutó la pieza con las dos manos de manera satisfactoria, hay que seguir solfeando con él  mientras toca, a veces toca notas demás en la izquierda. Y confunde el Final de vez en cuando.</v>
+        <v xml:space="preserve">Trabajamos legato en ambos brazos. </v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v/>
+        <v>Lorena</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">25. Vieille Chanson - Gurlit </v>
+        <v>Swan Lake Waltz - Tchaikovsky</v>
       </c>
       <c r="C23" t="str">
         <v xml:space="preserve">Simultaneidad </v>
       </c>
       <c r="D23" t="str">
-        <v>4</v>
+        <v>1-16</v>
       </c>
       <c r="E23" t="str">
-        <v xml:space="preserve">Hay que recordarle que repita la primera parte dos veces seguidas. Ejecutó bien la mayor parte de la pieza,  hay que hacer énfasis en el legato y en el quinto de la izquierda., </v>
+        <v xml:space="preserve">NO VINO, Está tocando bastante bien, los saltos de la izquierda los hace de manera fluida. Seguimos con la introducción, que es una especie de escala. , Ya terminó el Vals. </v>
       </c>
     </row>
     <row r="24">
@@ -786,38 +771,38 @@
         <v/>
       </c>
       <c r="B24" t="str">
-        <v xml:space="preserve">Ejercicio Acorde Fm - Cm 1ra Inversión </v>
+        <v>Aura Lee - George Poulton</v>
       </c>
       <c r="C24" t="str">
-        <v>Acordes</v>
+        <v>Simultaneidad</v>
+      </c>
+      <c r="D24" t="str">
+        <v>1-16</v>
       </c>
       <c r="E24" t="str">
-        <v>Repasó los acordes en legato en forma de arpegios. Debe tener cuidado con el quinto(Que se apoye con el movimiento del brazo para no lastimarse). , En la mano derecha estamos complementando con la Dominante y Tercera.</v>
+        <v xml:space="preserve">Repasamos a 4 manos la primera página de manera satisfactoria.  Y también tocó la segunda página con el niño., </v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Majo</v>
+        <v/>
       </c>
       <c r="B25" t="str">
-        <v xml:space="preserve">Serenata - Schubert </v>
+        <v>Thousand Years - A Thousand Years</v>
       </c>
       <c r="C25" t="str">
-        <v xml:space="preserve">Simultaneidad </v>
-      </c>
-      <c r="D25" t="str">
-        <v>1-32</v>
+        <v>Simultaneidad - Christina Perri</v>
       </c>
       <c r="E25" t="str">
-        <v>Debe seguir repasando el compás 26, que tiene una gran dificultad, de resto, lleva bien la pieza, es muy recomendable que la siga repasando.</v>
+        <v>Ejecutó bien la primera página, resolvió bien el pivoteo con mano izquierda en la segunda página.</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v/>
+        <v>Lorenzo</v>
       </c>
       <c r="B26" t="str">
-        <v>La Vie en rose -  Édith Piaf</v>
+        <v>Harry Potter, Jhon Williams</v>
       </c>
       <c r="C26" t="str">
         <v>Simultaneidad</v>
@@ -826,7 +811,7 @@
         <v>1-8</v>
       </c>
       <c r="E26" t="str">
-        <v>DEBE REPASARLA. Estamos viendo la primera página, haciendo énfasis en la lectura. Debe tener cuidado con las voces internas.</v>
+        <v xml:space="preserve">Trabajamos segunda parte(compás 18) con manos unidas, en la izquierda solo va a hacer intervalos., , </v>
       </c>
     </row>
     <row r="27">
@@ -834,67 +819,67 @@
         <v/>
       </c>
       <c r="B27" t="str">
-        <v xml:space="preserve"> Danza Húngara No. 5 - Johannes Brahms </v>
+        <v>Aura Lee</v>
       </c>
       <c r="C27" t="str">
-        <v>Simultaneidad - Dinámicas - Ritmo</v>
+        <v>Simultaniedad</v>
       </c>
       <c r="D27" t="str">
-        <v>1-8</v>
+        <v>1-4</v>
       </c>
       <c r="E27" t="str">
-        <v>Debe tener cuidado de no pararse tocando más lento. Estamos empezando tercer sistema con dos manos, le estoy pidiendo que toque muy lento las semicorcheas. Ya empezamos segunda parte solo con manos separadas.</v>
+        <v>Solo repasó(por que había faltado dos clases) con dos manos acompañado de su profesor el primer sistema, permitiéndole hacer énfasis en el ritmo. Sin embargo le cuesta motivarse con la pieza.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Martin_Rosero</v>
+        <v/>
       </c>
       <c r="B28" t="str">
-        <v>Oompa Loompa - Leslie Bricusse, Anthony Newley</v>
+        <v>Jurassic Park</v>
       </c>
       <c r="C28" t="str">
-        <v>Simultaneidad - Ritmo</v>
+        <v>Simultaneidad</v>
       </c>
       <c r="D28" t="str">
-        <v>1-12</v>
+        <v>1-4</v>
       </c>
       <c r="E28" t="str">
-        <v>NO VINO, Avanzó la segunda parte debe estar muy claro con las notas de la mano izquierda.(Me informa que no tiene teclado en este momento)</v>
+        <v>Repasamos el motivo principal de la pieza usando dos manos, nos falta darle un final adecuado para el,  podría s er los últimos tres compases de la pieza.</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v/>
+        <v>Majo</v>
       </c>
       <c r="B29" t="str">
-        <v xml:space="preserve">Jurassic Park - John Williams </v>
+        <v xml:space="preserve">Serenata - Schubert </v>
       </c>
       <c r="C29" t="str">
-        <v>Simultaneidad</v>
+        <v xml:space="preserve">Simultaneidad </v>
       </c>
       <c r="D29" t="str">
-        <v>1-4</v>
+        <v>1-32</v>
       </c>
       <c r="E29" t="str">
-        <v xml:space="preserve">Repasamos el primer sistema haciendo énfasis en el tema principal.  Empezó a trabajar la segunda con dos manos. </v>
+        <v>Debe seguir repasando el compás 26, que tiene una gran dificultad, de resto, lleva bien la pieza, es muy recomendable que la siga repasando.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Martin_Yañez</v>
+        <v/>
       </c>
       <c r="B30" t="str">
-        <v>Everybody Wants to Rule The World - Tears for Fears</v>
+        <v>La Vie en rose -  Édith Piaf</v>
       </c>
       <c r="C30" t="str">
         <v>Simultaneidad</v>
       </c>
       <c r="D30" t="str">
-        <v>1-4</v>
+        <v>1-8</v>
       </c>
       <c r="E30" t="str">
-        <v>NO VINO, Repasó las dos primeras partes de la pieza, con la variación en la segunda parte que pudimos repasar satisfactoriamente. Debe seguir estudiando. Siempre cuidando digitación.</v>
+        <v>DEBE REPASARLA. Estamos viendo la primera página, haciendo énfasis en la lectura. Debe tener cuidado con las voces internas.</v>
       </c>
     </row>
     <row r="31">
@@ -902,33 +887,33 @@
         <v/>
       </c>
       <c r="B31" t="str">
-        <v xml:space="preserve">Minuet in C, Op 1 - Alexander Reinagle </v>
+        <v xml:space="preserve"> Danza Húngara No. 5 - Johannes Brahms </v>
       </c>
       <c r="C31" t="str">
-        <v>Simultaneidad</v>
+        <v>Simultaneidad - Dinámicas - Ritmo</v>
       </c>
       <c r="D31" t="str">
-        <v>1-4</v>
+        <v>1-8</v>
       </c>
       <c r="E31" t="str">
-        <v xml:space="preserve"> Debe practicar más. Ejecutó bien el primer sistema con dos manos.  </v>
+        <v>Vamos en la segunda parte con ambas manos. (Esta tocando más lento, lo cual me parece muy positivo)</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Maximiliano</v>
+        <v>Martin_Rosero</v>
       </c>
       <c r="B32" t="str">
-        <v>Danza Antigua - Etude Debutants</v>
+        <v>Oompa Loompa - Leslie Bricusse, Anthony Newley</v>
       </c>
       <c r="C32" t="str">
-        <v>Simultaneidad</v>
+        <v>Simultaneidad - Ritmo</v>
       </c>
       <c r="D32" t="str">
-        <v>1-16</v>
+        <v>1-12</v>
       </c>
       <c r="E32" t="str">
-        <v xml:space="preserve">Repasó toda la pieza,  buen uso del brazo, debe tener cuidado con el final. Tiene que repasar todo para mejorar la fluidez. </v>
+        <v xml:space="preserve">Repaso la segunda parte llegamos hasta el compás 16, ya le falta poco para terminar la pieza. Debemos seguir repasando insistentemente por que no tiene piano en su casa., </v>
       </c>
     </row>
     <row r="33">
@@ -936,33 +921,33 @@
         <v/>
       </c>
       <c r="B33" t="str">
-        <v>Aura Lee, George Poulton</v>
+        <v xml:space="preserve">Jurassic Park - John Williams </v>
       </c>
       <c r="C33" t="str">
         <v>Simultaneidad</v>
       </c>
       <c r="D33" t="str">
-        <v>1-4</v>
+        <v>1-16</v>
       </c>
       <c r="E33" t="str">
-        <v xml:space="preserve">Repasamos la primera página. Le falta fluidez al final. Debe repasar. Pudo ejecutar el primer sistema de la segunda página, debe repasar., , </v>
+        <v>Repasó con éxito toda la pieza, nos concentramos en trabajar los intervalos de la mano izquierda y el ritmo.</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Natalia</v>
+        <v/>
       </c>
       <c r="B34" t="str">
-        <v>Harry Potter (Tema Principal) - John Williams</v>
+        <v>Dark Vader</v>
       </c>
       <c r="C34" t="str">
-        <v>Simultaneidad - Dinámicas</v>
+        <v>Ritmo</v>
       </c>
       <c r="D34" t="str">
-        <v>1-20</v>
+        <v>1-4</v>
       </c>
       <c r="E34" t="str">
-        <v xml:space="preserve">NO VINO, Terminó la pieza, esta haciendo bien los arpegios en la izquierda, a veces corta un poco las notas largas, por eso hicimos un ejercicio de solfeo., También debe tener cuidado con el figuraje del algunas notas, a veces no les da el valor correcto. </v>
+        <v>Por ahora solo le estoy mostrando la pieza para ver si es de su agrado.</v>
       </c>
     </row>
     <row r="35">
@@ -970,33 +955,33 @@
         <v/>
       </c>
       <c r="B35" t="str">
-        <v>La Pantera Rosa</v>
+        <v>Shiny - Moana</v>
       </c>
       <c r="C35" t="str">
-        <v>Simultaniedad</v>
+        <v>Simultaneidad</v>
       </c>
       <c r="D35" t="str">
-        <v>1-16</v>
+        <v>1-8</v>
       </c>
       <c r="E35" t="str">
-        <v>Tocó toda la pieza. buen control del ritmo e interacción con la izquierda, la cual muestra una voz independiente descendente.    , En algunos segmentos de la pieza debe anticipar en la izquierda con ayuda de los silencios de corchea.</v>
+        <v>Estamos empezando a ver Shiny con mano derecha, enfocados en el motivo., Se estresa un poco con la mano derecha donde debe buscar más profundidad en el teclado. Le dije que trabajara el arpegio por partes y que llevara el 5to dedo más al fondo del teclado., https://youtu.be/eTqvzn8vr7k?si=E9yFheaYUCvK2bo8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Nicolas_Miro</v>
+        <v>Martin_Yañez</v>
       </c>
       <c r="B36" t="str">
-        <v>Bella Ciao - Mishka Ziganoff</v>
+        <v xml:space="preserve">Quinta Recreación - Carpentier </v>
       </c>
       <c r="C36" t="str">
         <v>Simultaneidad</v>
       </c>
       <c r="D36" t="str">
-        <v>1-4</v>
+        <v>1-8</v>
       </c>
       <c r="E36" t="str">
-        <v>Repasamos segunda parte los primeros compases, debe estar pendiente de los cambios de la izquierda para la segunda parte. Le falta repasar el final de la segunda parte.</v>
+        <v xml:space="preserve">Terminó la primera y segunda parte , pero hay que repasar con constancia para que realmente suene fluido. Le cuesta un poco el cambio de acorde(tercer dedo de mano izquierda) pero lo está haciendo bastante bien., </v>
       </c>
     </row>
     <row r="37">
@@ -1004,33 +989,33 @@
         <v/>
       </c>
       <c r="B37" t="str">
-        <v>Clint Eastwood - Gorillaz</v>
+        <v>Danza de Lutins</v>
       </c>
       <c r="C37" t="str">
-        <v>Simultaneidad - Ritmo</v>
+        <v>Fraseo</v>
       </c>
       <c r="D37" t="str">
-        <v>1-14</v>
+        <v>1-8</v>
       </c>
       <c r="E37" t="str">
-        <v>Repasó los dos primeros sistemas. Ha mejorado mucho la introducción y el ritmo en general, bastante fluido, a veces se confunde con los bajos, debe estar pendiente. Está tocando la tercera parte bastante bien.</v>
+        <v>Trabajó muy bien con mano derecha e izquieda el motivo principal.Haciendo buen uso de brazo.</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Nicolas_Rivera</v>
+        <v>Maximiliano</v>
       </c>
       <c r="B38" t="str">
-        <v>Danza Rusa - Etude Debuntants</v>
+        <v>Danza Antigua - Etude Debutants</v>
       </c>
       <c r="C38" t="str">
         <v>Simultaneidad</v>
       </c>
       <c r="D38" t="str">
-        <v>1-8</v>
+        <v>1-16</v>
       </c>
       <c r="E38" t="str">
-        <v xml:space="preserve">Esta tocando bien toda la pieza, y sigue el ritmo con su profesor., , Hay que seguirle recordando el problema con los dedos pegados., , </v>
+        <v xml:space="preserve">Repasó toda la pieza,  buen uso del brazo, debe tener cuidado con el final. Tiene que repasar todo para mejorar la fluidez. </v>
       </c>
     </row>
     <row r="39">
@@ -1038,33 +1023,33 @@
         <v/>
       </c>
       <c r="B39" t="str">
-        <v>19. Pas Vite - Etude Debutants</v>
+        <v>Aura Lee, George Poulton</v>
       </c>
       <c r="C39" t="str">
-        <v>Monodia - Legato</v>
+        <v>Simultaneidad</v>
       </c>
       <c r="D39" t="str">
-        <v>1-8</v>
+        <v>1-4</v>
       </c>
       <c r="E39" t="str">
-        <v xml:space="preserve">Terminó la pieza, ya está tocando con mas precisión(pero debe seguir practicando), se frustra un poco cuando no le salen las cosas, debe estar muy pendiente de la digitación. , , </v>
+        <v xml:space="preserve">Ejecutó toda la pieza, se confunde un poco al final sobre todo con el último compás en el Si., , </v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Ramiro</v>
+        <v>Natalia</v>
       </c>
       <c r="B40" t="str">
-        <v>Marcha Imperial - John Williams</v>
+        <v>Muestrate - Robert Lopez</v>
       </c>
       <c r="C40" t="str">
-        <v>Simultaneidad</v>
+        <v>Simultaneidad - Dinámicas</v>
       </c>
       <c r="D40" t="str">
-        <v>1-12</v>
+        <v>1-25</v>
       </c>
       <c r="E40" t="str">
-        <v xml:space="preserve">Seguimos con tercer sistema,  hay que tener mucho cuidado que lo haga legato, no debe levantar brazo, puede ser una parte difícil de recordar. Para la izquierda le voy a colocar un solo acorde por cada compás ya que tiene constante dificultad para su ejecución(En esta parte debe tener mucho cuidado de respetar la digitación de la derecha). Pudo ejecutar los dos primeros compases de la tercera parte., </v>
+        <v xml:space="preserve">NO VINO, Repasó la pieza, debe enfocarse más en el final y el uso de dinámicas., , También debe tener cuidado con el figuraje del algunas notas, a veces no les da el valor correcto. , , Al finalizar hay que trabajar el tema de las dinámicas. , </v>
       </c>
     </row>
     <row r="41">
@@ -1072,33 +1057,33 @@
         <v/>
       </c>
       <c r="B41" t="str">
-        <v>Galop Favori - A Le Carpentier</v>
+        <v>Un mundo ideal - Alan Menken</v>
       </c>
       <c r="C41" t="str">
-        <v>Simultaneidad</v>
+        <v>Simultaniedad</v>
       </c>
       <c r="D41" t="str">
-        <v>1-4</v>
+        <v>1-16</v>
       </c>
       <c r="E41" t="str">
-        <v>Repasó la pieza, pero hay que trabajar muy lentamente esos pequeños puentes hasta llegar al final.</v>
+        <v xml:space="preserve">Trabajó bastante bien los arpegios de la mano izquierda y la anticipación., La segunda parte la está trabajando bastante bien, esta tocando bien los acordes.,  , </v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Samuel</v>
+        <v>Nicolas_Miro</v>
       </c>
       <c r="B42" t="str">
-        <v>Danza Rusa</v>
+        <v>Bella Ciao - Mishka Ziganoff</v>
       </c>
       <c r="C42" t="str">
-        <v>Monodia - Legato</v>
+        <v>Simultaneidad</v>
       </c>
       <c r="D42" t="str">
-        <v>1-8</v>
+        <v>1-4</v>
       </c>
       <c r="E42" t="str">
-        <v>Ejecutó toda la pieza bien, además lo acompaño su profesor practicando de esta forma el acompañamiento y como llevar efectivamente el tempo.</v>
+        <v>NO HUBO CLASE, Debe tener en cuenta la anticipación de la izquierda en la parte final. , Repasando el final de la segunda parte. Sobre todo debemos estar pendiente de los cambios con la izquierda(Le hice un video especial para eso)</v>
       </c>
     </row>
     <row r="43">
@@ -1106,16 +1091,16 @@
         <v/>
       </c>
       <c r="B43" t="str">
-        <v>19. Pas vite</v>
+        <v>Coro del Crociato</v>
       </c>
       <c r="C43" t="str">
-        <v>Simultaneidad</v>
+        <v>Ritmo</v>
       </c>
       <c r="D43" t="str">
         <v>1-4</v>
       </c>
       <c r="E43" t="str">
-        <v>Debe tener cuidado en  la izquierda con  el 5to pulgar.  Terminó la pieza. Debe seguir repasando.</v>
+        <v xml:space="preserve">TrabajamosSeguimos trabajando segundo sistema con manos unidas. Ya se siente más agusto con el ritmo.Trabajamos, Trabajó bien el motivo principal de la pieza con las dos manos e hizo el correcto valor de las notas, que puede ser un poco difícil al principio por los saltos., </v>
       </c>
     </row>
     <row r="44">
@@ -1123,21 +1108,226 @@
         <v/>
       </c>
       <c r="B44" t="str">
+        <v>Memories - Maroon 5</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Simultaneidad</v>
+      </c>
+      <c r="D44" t="str">
+        <v xml:space="preserve">1-8 </v>
+      </c>
+      <c r="E44" t="str">
+        <v xml:space="preserve">Trabajamos segundo sistema con manos unidas, es un poco dificil de lograr la independencia, entonces solo estamos haciendo acordes en la izquierda. </v>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
+        <v>Nicolas_Rivera</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Danse des Lutins</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Staccato</v>
+      </c>
+      <c r="D45" t="str">
+        <v>1-8</v>
+      </c>
+      <c r="E45" t="str" xml:space="preserve">
+        <v xml:space="preserve">
+Repasamos motivo principal con mano derecha, mostró interés por el ritmo.</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v/>
+      </c>
+      <c r="B46" t="str">
+        <v>Alouette</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Simultaneidad</v>
+      </c>
+      <c r="D46" t="str">
+        <v>1-4</v>
+      </c>
+      <c r="E46" t="str">
+        <v xml:space="preserve">Seguimos repasando toda la pieza para que pueda hacerlo mas fluido., Ejecutó bastante bien la primera parte, solo está haciendo cuarto dedo en la izquierda para evitar estrés. , Se le presenta la simultaniedad como un desafio., , </v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Ramiro</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Marcha Imperial - John Williams</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Simultaneidad</v>
+      </c>
+      <c r="D47" t="str">
+        <v>1-12</v>
+      </c>
+      <c r="E47" t="str">
+        <v xml:space="preserve">NO VINO, Seguimos con tercer sistema, Se le hizo un pequeño arreglo en la mano izquierda debido a la dificultad con la derecha, sin embargo debe estar muy pendiente del tiempo., , Incorporación de tocó legato en las últimas frases. , Ejecutó más a tempo la pieza, </v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v/>
+      </c>
+      <c r="B48" t="str">
+        <v>La Sala de Conversación - A Le Carpentier</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Simultaneidad</v>
+      </c>
+      <c r="D48" t="str">
+        <v>1-8</v>
+      </c>
+      <c r="E48" t="str">
+        <v xml:space="preserve">NO HUBO CLASE, Seguimos Trabajando la segunda parte del segundo sistema con manos unidas., Hay que hacer más acompañamiento con el., Repasó bien el primer sistema con las dos manos, debe practicar mas a tempo. , , </v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v/>
+      </c>
+      <c r="B49" t="str">
+        <v xml:space="preserve">Indiana Jones </v>
+      </c>
+      <c r="C49" t="str">
+        <v xml:space="preserve">Simultaneidad </v>
+      </c>
+      <c r="D49" t="str">
+        <v xml:space="preserve">1-8 </v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Samuel</v>
+      </c>
+      <c r="B50" t="str">
+        <v>19. Pas vite</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Simultaneidad</v>
+      </c>
+      <c r="D50" t="str">
+        <v>1-4</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Debe tener cuidado en  la izquierda con  el 5to pulgar.  Terminó la pieza. Debe seguir repasando.</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v/>
+      </c>
+      <c r="B51" t="str">
         <v>Danza en C Mayor - Gurlitt</v>
       </c>
-      <c r="C44" t="str">
+      <c r="C51" t="str">
         <v xml:space="preserve">Simultaneidad </v>
       </c>
-      <c r="D44" t="str">
-        <v>1-4</v>
-      </c>
-      <c r="E44" t="str">
-        <v>Repasó con éxito los primeros compases, debe tener mucho cuidado con el uso del brazo, tercer dedo en la izquierda y pulgar. Debe repasar los últimos  2 compases del sistema con las dos manos.</v>
+      <c r="D51" t="str">
+        <v>1-4</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Trabajó bastante bien a dos manos y el legato de 5 notas. Trababó bastante bien los intervalos en la mano izquierda, ya que hacer los acordes presentan cierta dificultad.</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v/>
+      </c>
+      <c r="B52" t="str">
+        <v>Pequeños compañeros - Chwatal</v>
+      </c>
+      <c r="C52" t="str">
+        <v xml:space="preserve">Simultaneidad </v>
+      </c>
+      <c r="D52" t="str">
+        <v>1-8</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Seguimos trabajando a dos manos y el legato de 5 notas. Trababó bastante bien los intervalos en la mano izquierda, ya que hacer los acordes presentan cierta dificultad.</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Tomas</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Pas Vite</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Legato y Portato</v>
+      </c>
+      <c r="D53" t="str">
+        <v>1-4</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Trabajó muy bien el uso del brazo, y el legato de tres notas., , Tocó la pieza de manera exitosa acompañado de su profesor. Debe hacer más ejercicios de fuerza o de brazo. (Cada dedo de manera separada con brazo)</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v/>
+      </c>
+      <c r="B54" t="str">
+        <v>Dance en do mayor - Gurlitt</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Legato</v>
+      </c>
+      <c r="D54" t="str">
+        <v>1-8</v>
+      </c>
+      <c r="E54" t="str">
+        <v xml:space="preserve">Debemos seguir trabajando la mano izquierda por que le cuesta hacer 5to dedo., Estamos trabajando bien la correcta posición de los dedos al momento de hacer legatos. Está tocando bien de la tecla hacia abajo. , </v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v/>
+      </c>
+      <c r="B55" t="str">
+        <v>Danse de Lutins</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Fraseo</v>
+      </c>
+      <c r="D55" t="str">
+        <v>1-8</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Trabajó bien el motivo principal y su respectiva respuesta, ejecutó muy bien el legato de tres notas.</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v/>
+      </c>
+      <c r="B56" t="str">
+        <v>Danza Rusa</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Legato</v>
+      </c>
+      <c r="D56" t="str">
+        <v>1-8</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Trabajó muy bien el Legato de tres notas acompañado de su profesor.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E56"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/estudiantes.xlsx
+++ b/estudiantes.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E42"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,7 +430,7 @@
         <v>1-8</v>
       </c>
       <c r="E2" t="str">
-        <v xml:space="preserve">Ejecutó muy bien el Legato de 3 notas, haciendo buen uso del brazo., Tocó la pieza acompañada de su profesor. </v>
+        <v xml:space="preserve">Ejecutó muy bien el Legato de 3 notas, haciendo buen uso del brazo(gesto de liberación)., Tocó la pieza acompañada de su profesor. </v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         <v>1-8</v>
       </c>
       <c r="E4" t="str">
-        <v xml:space="preserve">NO VINO, Repasamos la primera parte de la pieza, tenía tiempo sin venir., Mejoró mucho la anticipación y ejecución en el compás 11 con el acorde de la mano derecha, debe tener mucho cuidado con la digitación y no correr., Llegamos a la parte donde se alternan las manos, lo estoy acompañando con la voz., Repasamos la ejecución de los acordes de ambas manos en el primer sistema y el uso de las octavas. , , </v>
+        <v xml:space="preserve">Llegamos al final de la pieza, lo está haciendo muy bien, debemos tener cuidado con el tempo., Mejoró mucho la anticipación y ejecución en el compás 11 con el acorde de la mano derecha, debe tener mucho cuidado con la digitación y no correr., , </v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +503,7 @@
         <v>1-8</v>
       </c>
       <c r="E7" t="str">
-        <v xml:space="preserve">Terminando el tercer sistema, está trabajando bien relación 5to-Pulgar con mas confianza. Y ha trabajado bien la dificultad de la polifonía., , , </v>
+        <v xml:space="preserve">Ha terminado el primer sistema pero debe trabajar mucho la anticipación para lograr una fluidez mínima deseada. La veo un poco  nerviosa al momento de grabar . Propongo que traté de tocar más para sus familiares y amigos cuando cuente con el tiempo. , , , </v>
       </c>
     </row>
     <row r="8">
@@ -517,7 +517,7 @@
         <v xml:space="preserve">Simultaneidad </v>
       </c>
       <c r="D8" t="str">
-        <v>1-7</v>
+        <v>1-16</v>
       </c>
       <c r="E8" t="str">
         <v xml:space="preserve">Terminó la pieza pero debe tener cuidado con el figuraje del tema principal y los cambios en la armonía, sobre todo al final. </v>
@@ -537,7 +537,7 @@
         <v>1-8</v>
       </c>
       <c r="E9" t="str">
-        <v>Trabajamos hasta segundo sistema lentamente, ha entendido muy bien el motivo principal.</v>
+        <v xml:space="preserve">Repasamos segundo sistema, le cuesta los cambios tanto en la izquierda como la derecha(le confunde la melodía pero no por dificultad técnica, más bien por que no le parece tan intuitiva, debe escucharla con más atención),  es muy importante que practique más para conseguir tocar con más fluidez. Debe de concentrarse más en estudiar esa segunda parte </v>
       </c>
     </row>
     <row r="10">
@@ -554,7 +554,7 @@
         <v>1-4</v>
       </c>
       <c r="E10" t="str">
-        <v>Ejecutó bien la segunda parte de la pieza, que es un poco mas sencilla. Esta haciendo muy bien la simultaneidad, y correcto uso de 5to dedo.</v>
+        <v>Terminó la pieza, debe esforzarse por recordar la posición de los dedos al empezar la pieza. Uso correcto uso de 5to dedo.</v>
       </c>
     </row>
     <row r="11">
@@ -571,7 +571,7 @@
         <v>1-4</v>
       </c>
       <c r="E11" t="str">
-        <v>Ejecutó bien el motivo principal con dos manos. Debe repasar para empezar el segundo sistema.</v>
+        <v xml:space="preserve">Empezamos tercer sistema, ejecutó bien los dos primeros sistemas, pero debe repasar más para tener seguridad. </v>
       </c>
     </row>
     <row r="12">
@@ -621,19 +621,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jeronimo</v>
+        <v>Juan_Camilo</v>
       </c>
       <c r="B15" t="str">
-        <v>Everybody wants to Rule the World - Tears for Fears</v>
+        <v>Beethoven 5</v>
       </c>
       <c r="C15" t="str">
-        <v>Simultaneidad</v>
+        <v>Simultaneidad - Dinámicas</v>
       </c>
       <c r="D15" t="str">
-        <v>1-4</v>
+        <v>1-32</v>
       </c>
       <c r="E15" t="str">
-        <v xml:space="preserve">NO VINO, Repasó las dos primeras partes de la pieza, con la variación en la segunda parte que pudimos repasar satisfactoriamente. Debe seguir estudiando. Siempre cuidando digitación., </v>
+        <v xml:space="preserve">Terminamos la pieza, es necesario seguir trabajando la pieza concentrados en el tempo y cuidando la digitación., Continuamos trabajando haciendo énfasis en los acentos que debe hacer para no perder el ritmo de la pieza., Trabajó bastante bien a dos manos, hicimos énfasis en el tempo., , </v>
       </c>
     </row>
     <row r="16">
@@ -641,33 +641,27 @@
         <v/>
       </c>
       <c r="B16" t="str">
-        <v>Yo te extrañaré - Canción del tercer Cielo</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Simultaneidad</v>
-      </c>
-      <c r="D16" t="str">
-        <v>1-4</v>
+        <v>Cuatro Estaciones de Vivaldi</v>
       </c>
       <c r="E16" t="str">
-        <v>Trabajamos armonía, pudo ejecutar los 3 primeros acordes(en realidad intervalos) con la mano izquierda.  Ejecutó toda la pieza, pero debe practicar mucho.</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Juan_Camilo</v>
+        <v/>
       </c>
       <c r="B17" t="str">
-        <v>Beethoven 5</v>
+        <v xml:space="preserve">Titanic </v>
       </c>
       <c r="C17" t="str">
-        <v>Simultaneidad - Dinámicas</v>
+        <v>Simultaneidad</v>
       </c>
       <c r="D17" t="str">
-        <v>1-32</v>
+        <v>1-16</v>
       </c>
       <c r="E17" t="str">
-        <v xml:space="preserve">NO VA A VENIR HASTA EL 24, Terminamos la pieza, es necesario seguir trabajando la pieza concentrados en el tempo y cuidando la digitación., Continuamos trabajando haciendo énfasis en los acentos que debe hacer para no perder el ritmo de la pieza., Trabajó bastante bien a dos manos, hicimos énfasis en el tempo., , </v>
+        <v>Trabajamos los dos primeros sistema. Se la está aprendiendo con relativa rapidez, pero es necesario que repase en casa para asegurar. Está haciendo muy bien los cambios en la izquierda. Hay que cuidar mucho la digitación.</v>
       </c>
     </row>
     <row r="18">
@@ -675,18 +669,24 @@
         <v/>
       </c>
       <c r="B18" t="str">
-        <v>Cuatro Estaciones de Vivaldi</v>
+        <v>Jurassic Park</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Simultaniedad</v>
+      </c>
+      <c r="D18" t="str">
+        <v>1-12</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>Terminó la pieza. Debe seguir repasando.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v/>
+        <v>Lorenzo</v>
       </c>
       <c r="B19" t="str">
-        <v xml:space="preserve">Titanic </v>
+        <v>Harry Potter, Jhon Williams</v>
       </c>
       <c r="C19" t="str">
         <v>Simultaneidad</v>
@@ -695,7 +695,7 @@
         <v>1-8</v>
       </c>
       <c r="E19" t="str">
-        <v xml:space="preserve">Trabajamos los dos primeros sistema. Es necesario trabajar más con los acordes. </v>
+        <v xml:space="preserve">Trabajamos toda la pieza, debe cuidar no esconder los dedos de la mano izquierda, en la izquierda solo va a hacer intervalos., , </v>
       </c>
     </row>
     <row r="20">
@@ -703,84 +703,84 @@
         <v/>
       </c>
       <c r="B20" t="str">
-        <v>Jurassic Park</v>
+        <v>Aura Lee</v>
       </c>
       <c r="C20" t="str">
         <v>Simultaniedad</v>
       </c>
       <c r="D20" t="str">
-        <v>1-12</v>
+        <v>1-8</v>
       </c>
       <c r="E20" t="str">
-        <v>Terminó la pieza. Debe seguir repasando.</v>
+        <v>Repasó con dos manos acompañado de su profesor, permitiéndole hacer énfasis en el ritmo. Sin embargo le cuesta motivarse con la pieza(Solo tocaremos hasta el tercer sistema.).</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Juan_Pablo</v>
+        <v/>
       </c>
       <c r="B21" t="str">
-        <v>20. Avec Doceur - Etude Debutants</v>
+        <v>Jurassic Park</v>
       </c>
       <c r="C21" t="str">
-        <v>Legato - Brazo</v>
+        <v>Simultaneidad</v>
       </c>
       <c r="D21" t="str">
-        <v>1-8</v>
+        <v>1-4</v>
       </c>
       <c r="E21" t="str">
-        <v>Debe anticipar las manos y no bajarlas tanto., , Trabajó Legato en ambas manos. La ejecutó toda pero le falta practicar más el final, y escucharla en su totalidad.</v>
+        <v>Repasamos  la pieza usando dos manos, nos falta darle un final adecuado para el,  podría s er los últimos tres compases de la pieza.</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v/>
+        <v>Martin_Rosero</v>
       </c>
       <c r="B22" t="str">
-        <v>Fiesta de Cumpleaños, Thompson</v>
+        <v>Oompa Loompa - Leslie Bricusse, Anthony Newley</v>
       </c>
       <c r="C22" t="str">
-        <v>Legato - Brazo</v>
+        <v>Simultaneidad - Ritmo</v>
       </c>
       <c r="D22" t="str">
-        <v>1-4</v>
+        <v>1-12</v>
       </c>
       <c r="E22" t="str">
-        <v xml:space="preserve">Trabajamos legato en ambos brazos. </v>
+        <v xml:space="preserve">Ejecutó toda la pieza, pero le falta mas fluidez.  Debemos seguir repasando insistentemente por que  no tiene piano en su casa., </v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Lorena</v>
+        <v/>
       </c>
       <c r="B23" t="str">
-        <v>Swan Lake Waltz - Tchaikovsky</v>
+        <v xml:space="preserve">Jurassic Park - John Williams </v>
       </c>
       <c r="C23" t="str">
-        <v xml:space="preserve">Simultaneidad </v>
+        <v>Simultaneidad</v>
       </c>
       <c r="D23" t="str">
         <v>1-16</v>
       </c>
       <c r="E23" t="str">
-        <v xml:space="preserve">NO VINO, Está tocando bastante bien, los saltos de la izquierda los hace de manera fluida. Seguimos con la introducción, que es una especie de escala. , Ya terminó el Vals. </v>
+        <v>Repasó con éxito toda la pieza, nos concentramos en trabajar los intervalos de la mano izquierda y el ritmo.  No tiene piano en su casa.</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v>Martin_Yañez</v>
       </c>
       <c r="B24" t="str">
-        <v>Aura Lee - George Poulton</v>
+        <v xml:space="preserve">Quinta Recreación - Carpentier </v>
       </c>
       <c r="C24" t="str">
         <v>Simultaneidad</v>
       </c>
       <c r="D24" t="str">
-        <v>1-16</v>
+        <v>1-8</v>
       </c>
       <c r="E24" t="str">
-        <v xml:space="preserve">Repasamos a 4 manos la primera página de manera satisfactoria.  Y también tocó la segunda página con el niño., </v>
+        <v xml:space="preserve">No Vino, Terminó la primera y segunda parte , pero hay que repasar con constancia para que realmente suene fluido. Le cuesta un poco el cambio de acorde(tercer dedo de mano izquierda) pero lo está haciendo bastante bien., </v>
       </c>
     </row>
     <row r="25">
@@ -788,30 +788,33 @@
         <v/>
       </c>
       <c r="B25" t="str">
-        <v>Thousand Years - A Thousand Years</v>
+        <v>Danza de Lutins</v>
       </c>
       <c r="C25" t="str">
-        <v>Simultaneidad - Christina Perri</v>
+        <v>Fraseo</v>
+      </c>
+      <c r="D25" t="str">
+        <v>1-8</v>
       </c>
       <c r="E25" t="str">
-        <v>Ejecutó bien la primera página, resolvió bien el pivoteo con mano izquierda en la segunda página.</v>
+        <v>Trabajó muy bien con mano derecha e izquieda el motivo principal.Haciendo buen uso de brazo.</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Lorenzo</v>
+        <v>Natalia</v>
       </c>
       <c r="B26" t="str">
-        <v>Harry Potter, Jhon Williams</v>
+        <v>Muestrate - Robert Lopez</v>
       </c>
       <c r="C26" t="str">
-        <v>Simultaneidad</v>
+        <v>Simultaneidad - Dinámicas</v>
       </c>
       <c r="D26" t="str">
-        <v>1-8</v>
+        <v>1-25</v>
       </c>
       <c r="E26" t="str">
-        <v xml:space="preserve">Trabajamos segunda parte(compás 18) con manos unidas, en la izquierda solo va a hacer intervalos., , </v>
+        <v xml:space="preserve">NO VINO, Repasó la pieza, debe enfocarse más en el final y el uso de dinámicas., , También debe tener cuidado con el figuraje del algunas notas, a veces no les da el valor correcto. , , Al finalizar hay que trabajar el tema de las dinámicas. , </v>
       </c>
     </row>
     <row r="27">
@@ -819,24 +822,24 @@
         <v/>
       </c>
       <c r="B27" t="str">
-        <v>Aura Lee</v>
+        <v>Un mundo ideal - Alan Menken</v>
       </c>
       <c r="C27" t="str">
         <v>Simultaniedad</v>
       </c>
       <c r="D27" t="str">
-        <v>1-4</v>
+        <v>1-16</v>
       </c>
       <c r="E27" t="str">
-        <v>Solo repasó(por que había faltado dos clases) con dos manos acompañado de su profesor el primer sistema, permitiéndole hacer énfasis en el ritmo. Sin embargo le cuesta motivarse con la pieza.</v>
+        <v xml:space="preserve">Trabajó bastante bien los arpegios de la mano izquierda y la anticipación., La segunda parte la está trabajando bastante bien, esta tocando bien los acordes.,  , </v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v/>
+        <v>Nicolas_Miro</v>
       </c>
       <c r="B28" t="str">
-        <v>Jurassic Park</v>
+        <v>Bella Ciao - Mishka Ziganoff</v>
       </c>
       <c r="C28" t="str">
         <v>Simultaneidad</v>
@@ -845,24 +848,24 @@
         <v>1-4</v>
       </c>
       <c r="E28" t="str">
-        <v>Repasamos el motivo principal de la pieza usando dos manos, nos falta darle un final adecuado para el,  podría s er los últimos tres compases de la pieza.</v>
+        <v>Debemos estar pendiente de los cambios con la izquierda.</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Majo</v>
+        <v/>
       </c>
       <c r="B29" t="str">
-        <v xml:space="preserve">Serenata - Schubert </v>
+        <v>Coro del Crociato - Adolf Le Carpentier</v>
       </c>
       <c r="C29" t="str">
-        <v xml:space="preserve">Simultaneidad </v>
+        <v>Ritmo</v>
       </c>
       <c r="D29" t="str">
-        <v>1-32</v>
+        <v>1-16</v>
       </c>
       <c r="E29" t="str">
-        <v>Debe seguir repasando el compás 26, que tiene una gran dificultad, de resto, lleva bien la pieza, es muy recomendable que la siga repasando.</v>
+        <v xml:space="preserve">Estamos trabajando tercer sistema con manos unidas. Ya se siente más cómodo con el ritmo. , , </v>
       </c>
     </row>
     <row r="30">
@@ -870,67 +873,68 @@
         <v/>
       </c>
       <c r="B30" t="str">
-        <v>La Vie en rose -  Édith Piaf</v>
+        <v>Memories - Maroon 5</v>
       </c>
       <c r="C30" t="str">
         <v>Simultaneidad</v>
       </c>
       <c r="D30" t="str">
-        <v>1-8</v>
+        <v xml:space="preserve">1-8 </v>
       </c>
       <c r="E30" t="str">
-        <v>DEBE REPASARLA. Estamos viendo la primera página, haciendo énfasis en la lectura. Debe tener cuidado con las voces internas.</v>
-      </c>
-    </row>
-    <row r="31">
+        <v xml:space="preserve">Trabajamos tercer sistema con manos unidas, solo estamos haciendo acordes en la izquierda. Ya terminó la pieza pero le falta practicar más el final. </v>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
       <c r="A31" t="str">
-        <v/>
+        <v>Nicolas_Rivera</v>
       </c>
       <c r="B31" t="str">
-        <v xml:space="preserve"> Danza Húngara No. 5 - Johannes Brahms </v>
+        <v>Danse des Lutins</v>
       </c>
       <c r="C31" t="str">
-        <v>Simultaneidad - Dinámicas - Ritmo</v>
+        <v>Legato</v>
       </c>
       <c r="D31" t="str">
         <v>1-8</v>
       </c>
-      <c r="E31" t="str">
-        <v>Vamos en la segunda parte con ambas manos. (Esta tocando más lento, lo cual me parece muy positivo)</v>
+      <c r="E31" t="str" xml:space="preserve">
+        <v xml:space="preserve">
+Empezamos segunda parte y repasamos la primera parte, mostró interés por el ritmo.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Martin_Rosero</v>
+        <v/>
       </c>
       <c r="B32" t="str">
-        <v>Oompa Loompa - Leslie Bricusse, Anthony Newley</v>
+        <v>Alouette</v>
       </c>
       <c r="C32" t="str">
-        <v>Simultaneidad - Ritmo</v>
+        <v>Simultaneidad</v>
       </c>
       <c r="D32" t="str">
-        <v>1-12</v>
+        <v>1-8</v>
       </c>
       <c r="E32" t="str">
-        <v xml:space="preserve">Repaso la segunda parte llegamos hasta el compás 16, ya le falta poco para terminar la pieza. Debemos seguir repasando insistentemente por que no tiene piano en su casa., </v>
+        <v xml:space="preserve">Ejecutó bastante bien la primera parte, solo está haciendo cuarto dedo en la izquierda para evitar estrés. , Se le presenta la simultaneidad como un desafió. Y no quiere que la pieza sea larga. , , </v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v/>
+        <v>Ramiro</v>
       </c>
       <c r="B33" t="str">
-        <v xml:space="preserve">Jurassic Park - John Williams </v>
+        <v>Marcha Imperial - John Williams</v>
       </c>
       <c r="C33" t="str">
         <v>Simultaneidad</v>
       </c>
       <c r="D33" t="str">
-        <v>1-16</v>
+        <v>1-12</v>
       </c>
       <c r="E33" t="str">
-        <v>Repasó con éxito toda la pieza, nos concentramos en trabajar los intervalos de la mano izquierda y el ritmo.</v>
+        <v xml:space="preserve">Ejecutó más a tempo la pieza, tocando la pieza acompañado de su profesor. , </v>
       </c>
     </row>
     <row r="34">
@@ -938,16 +942,16 @@
         <v/>
       </c>
       <c r="B34" t="str">
-        <v>Dark Vader</v>
+        <v>La Sala de Conversación - A. Le Carpentier</v>
       </c>
       <c r="C34" t="str">
-        <v>Ritmo</v>
+        <v>Simultaneidad</v>
       </c>
       <c r="D34" t="str">
-        <v>1-4</v>
+        <v>1-8</v>
       </c>
       <c r="E34" t="str">
-        <v>Por ahora solo le estoy mostrando la pieza para ver si es de su agrado.</v>
+        <v xml:space="preserve">Repasamos hasta el segundo sistema con manos unidas. Se le está acompañando usando solfeo. Hay que repetirle insistentemente que cuide la posición de su cuerpo.  , </v>
       </c>
     </row>
     <row r="35">
@@ -955,33 +959,33 @@
         <v/>
       </c>
       <c r="B35" t="str">
-        <v>Shiny - Moana</v>
+        <v xml:space="preserve">Indiana Jones </v>
       </c>
       <c r="C35" t="str">
-        <v>Simultaneidad</v>
+        <v xml:space="preserve">Simultaneidad </v>
       </c>
       <c r="D35" t="str">
-        <v>1-8</v>
+        <v xml:space="preserve">1-8 </v>
       </c>
       <c r="E35" t="str">
-        <v>Estamos empezando a ver Shiny con mano derecha, enfocados en el motivo., Se estresa un poco con la mano derecha donde debe buscar más profundidad en el teclado. Le dije que trabajara el arpegio por partes y que llevara el 5to dedo más al fondo del teclado., https://youtu.be/eTqvzn8vr7k?si=E9yFheaYUCvK2bo8</v>
+        <v xml:space="preserve">Empezamos primer sistema a dos manos con relativa facilidad, debe tener cuidado en donde debe acompañar adecuadamente con la izquierda.  </v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Martin_Yañez</v>
+        <v>Samuel</v>
       </c>
       <c r="B36" t="str">
-        <v xml:space="preserve">Quinta Recreación - Carpentier </v>
+        <v>19. Pas vite</v>
       </c>
       <c r="C36" t="str">
         <v>Simultaneidad</v>
       </c>
       <c r="D36" t="str">
-        <v>1-8</v>
+        <v>1-4</v>
       </c>
       <c r="E36" t="str">
-        <v xml:space="preserve">Terminó la primera y segunda parte , pero hay que repasar con constancia para que realmente suene fluido. Le cuesta un poco el cambio de acorde(tercer dedo de mano izquierda) pero lo está haciendo bastante bien., </v>
+        <v>Debe tener cuidado en  la izquierda con  el 5to pulgar.  Terminó la pieza. Debe seguir repasando.</v>
       </c>
     </row>
     <row r="37">
@@ -989,67 +993,67 @@
         <v/>
       </c>
       <c r="B37" t="str">
-        <v>Danza de Lutins</v>
+        <v>Danza en C Mayor - Gurlitt</v>
       </c>
       <c r="C37" t="str">
-        <v>Fraseo</v>
+        <v xml:space="preserve">Simultaneidad </v>
       </c>
       <c r="D37" t="str">
-        <v>1-8</v>
+        <v>1-4</v>
       </c>
       <c r="E37" t="str">
-        <v>Trabajó muy bien con mano derecha e izquieda el motivo principal.Haciendo buen uso de brazo.</v>
+        <v>Trabajó bastante bien a dos manos y el legato de 5 notas. Trababó bastante bien los intervalos en la mano izquierda, ya que hacer los acordes presentan cierta dificultad.</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Maximiliano</v>
+        <v/>
       </c>
       <c r="B38" t="str">
-        <v>Danza Antigua - Etude Debutants</v>
+        <v>Pequeños compañeros - Chwatal</v>
       </c>
       <c r="C38" t="str">
-        <v>Simultaneidad</v>
+        <v xml:space="preserve">Simultaneidad </v>
       </c>
       <c r="D38" t="str">
-        <v>1-16</v>
+        <v>1-8</v>
       </c>
       <c r="E38" t="str">
-        <v xml:space="preserve">Repasó toda la pieza,  buen uso del brazo, debe tener cuidado con el final. Tiene que repasar todo para mejorar la fluidez. </v>
+        <v>Seguimos trabajando a dos manos y el legato de 5 notas. Trababó bastante bien los intervalos en la mano izquierda, ya que hacer los acordes presentan cierta dificultad.</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v/>
+        <v>Tomas</v>
       </c>
       <c r="B39" t="str">
-        <v>Aura Lee, George Poulton</v>
+        <v>Pas Vite</v>
       </c>
       <c r="C39" t="str">
-        <v>Simultaneidad</v>
+        <v>Legato y Portato</v>
       </c>
       <c r="D39" t="str">
         <v>1-4</v>
       </c>
       <c r="E39" t="str">
-        <v xml:space="preserve">Ejecutó toda la pieza, se confunde un poco al final sobre todo con el último compás en el Si., , </v>
+        <v>Trabajó muy bien el uso del brazo, y el legato de tres notas., , Tocó la pieza de manera exitosa acompañado de su profesor. Debe hacer más ejercicios de fuerza o de brazo. (Cada dedo de manera separada con brazo)</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Natalia</v>
+        <v/>
       </c>
       <c r="B40" t="str">
-        <v>Muestrate - Robert Lopez</v>
+        <v>Dance en do mayor - Gurlitt</v>
       </c>
       <c r="C40" t="str">
-        <v>Simultaneidad - Dinámicas</v>
+        <v>Legato</v>
       </c>
       <c r="D40" t="str">
-        <v>1-25</v>
+        <v>1-8</v>
       </c>
       <c r="E40" t="str">
-        <v xml:space="preserve">NO VINO, Repasó la pieza, debe enfocarse más en el final y el uso de dinámicas., , También debe tener cuidado con el figuraje del algunas notas, a veces no les da el valor correcto. , , Al finalizar hay que trabajar el tema de las dinámicas. , </v>
+        <v xml:space="preserve">Trabajó muy bien  la mano izquierda, le cuesta hacer 5to dedo., Estamos trabajando bien la correcta posición de los dedos al momento de hacer legatos. Está tocando bien de la tecla hacia abajo. , </v>
       </c>
     </row>
     <row r="41">
@@ -1057,277 +1061,38 @@
         <v/>
       </c>
       <c r="B41" t="str">
-        <v>Un mundo ideal - Alan Menken</v>
+        <v>Danse de Lutins</v>
       </c>
       <c r="C41" t="str">
-        <v>Simultaniedad</v>
+        <v>Fraseo</v>
       </c>
       <c r="D41" t="str">
-        <v>1-16</v>
+        <v>1-8</v>
       </c>
       <c r="E41" t="str">
-        <v xml:space="preserve">Trabajó bastante bien los arpegios de la mano izquierda y la anticipación., La segunda parte la está trabajando bastante bien, esta tocando bien los acordes.,  , </v>
+        <v>Trabajó bien el motivo principal y su respectiva respuesta, ejecutó muy bien el legato de tres notas.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Nicolas_Miro</v>
+        <v/>
       </c>
       <c r="B42" t="str">
-        <v>Bella Ciao - Mishka Ziganoff</v>
+        <v>Danza Rusa</v>
       </c>
       <c r="C42" t="str">
-        <v>Simultaneidad</v>
+        <v>Legato</v>
       </c>
       <c r="D42" t="str">
-        <v>1-4</v>
+        <v>1-8</v>
       </c>
       <c r="E42" t="str">
-        <v>NO HUBO CLASE, Debe tener en cuenta la anticipación de la izquierda en la parte final. , Repasando el final de la segunda parte. Sobre todo debemos estar pendiente de los cambios con la izquierda(Le hice un video especial para eso)</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v/>
-      </c>
-      <c r="B43" t="str">
-        <v>Coro del Crociato</v>
-      </c>
-      <c r="C43" t="str">
-        <v>Ritmo</v>
-      </c>
-      <c r="D43" t="str">
-        <v>1-4</v>
-      </c>
-      <c r="E43" t="str">
-        <v xml:space="preserve">TrabajamosSeguimos trabajando segundo sistema con manos unidas. Ya se siente más agusto con el ritmo.Trabajamos, Trabajó bien el motivo principal de la pieza con las dos manos e hizo el correcto valor de las notas, que puede ser un poco difícil al principio por los saltos., </v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v/>
-      </c>
-      <c r="B44" t="str">
-        <v>Memories - Maroon 5</v>
-      </c>
-      <c r="C44" t="str">
-        <v>Simultaneidad</v>
-      </c>
-      <c r="D44" t="str">
-        <v xml:space="preserve">1-8 </v>
-      </c>
-      <c r="E44" t="str">
-        <v xml:space="preserve">Trabajamos segundo sistema con manos unidas, es un poco dificil de lograr la independencia, entonces solo estamos haciendo acordes en la izquierda. </v>
-      </c>
-    </row>
-    <row r="45" xml:space="preserve">
-      <c r="A45" t="str">
-        <v>Nicolas_Rivera</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Danse des Lutins</v>
-      </c>
-      <c r="C45" t="str">
-        <v>Staccato</v>
-      </c>
-      <c r="D45" t="str">
-        <v>1-8</v>
-      </c>
-      <c r="E45" t="str" xml:space="preserve">
-        <v xml:space="preserve">
-Repasamos motivo principal con mano derecha, mostró interés por el ritmo.</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v/>
-      </c>
-      <c r="B46" t="str">
-        <v>Alouette</v>
-      </c>
-      <c r="C46" t="str">
-        <v>Simultaneidad</v>
-      </c>
-      <c r="D46" t="str">
-        <v>1-4</v>
-      </c>
-      <c r="E46" t="str">
-        <v xml:space="preserve">Seguimos repasando toda la pieza para que pueda hacerlo mas fluido., Ejecutó bastante bien la primera parte, solo está haciendo cuarto dedo en la izquierda para evitar estrés. , Se le presenta la simultaniedad como un desafio., , </v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>Ramiro</v>
-      </c>
-      <c r="B47" t="str">
-        <v>Marcha Imperial - John Williams</v>
-      </c>
-      <c r="C47" t="str">
-        <v>Simultaneidad</v>
-      </c>
-      <c r="D47" t="str">
-        <v>1-12</v>
-      </c>
-      <c r="E47" t="str">
-        <v xml:space="preserve">NO VINO, Seguimos con tercer sistema, Se le hizo un pequeño arreglo en la mano izquierda debido a la dificultad con la derecha, sin embargo debe estar muy pendiente del tiempo., , Incorporación de tocó legato en las últimas frases. , Ejecutó más a tempo la pieza, </v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v/>
-      </c>
-      <c r="B48" t="str">
-        <v>La Sala de Conversación - A Le Carpentier</v>
-      </c>
-      <c r="C48" t="str">
-        <v>Simultaneidad</v>
-      </c>
-      <c r="D48" t="str">
-        <v>1-8</v>
-      </c>
-      <c r="E48" t="str">
-        <v xml:space="preserve">NO HUBO CLASE, Seguimos Trabajando la segunda parte del segundo sistema con manos unidas., Hay que hacer más acompañamiento con el., Repasó bien el primer sistema con las dos manos, debe practicar mas a tempo. , , </v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v/>
-      </c>
-      <c r="B49" t="str">
-        <v xml:space="preserve">Indiana Jones </v>
-      </c>
-      <c r="C49" t="str">
-        <v xml:space="preserve">Simultaneidad </v>
-      </c>
-      <c r="D49" t="str">
-        <v xml:space="preserve">1-8 </v>
-      </c>
-      <c r="E49" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>Samuel</v>
-      </c>
-      <c r="B50" t="str">
-        <v>19. Pas vite</v>
-      </c>
-      <c r="C50" t="str">
-        <v>Simultaneidad</v>
-      </c>
-      <c r="D50" t="str">
-        <v>1-4</v>
-      </c>
-      <c r="E50" t="str">
-        <v>Debe tener cuidado en  la izquierda con  el 5to pulgar.  Terminó la pieza. Debe seguir repasando.</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v/>
-      </c>
-      <c r="B51" t="str">
-        <v>Danza en C Mayor - Gurlitt</v>
-      </c>
-      <c r="C51" t="str">
-        <v xml:space="preserve">Simultaneidad </v>
-      </c>
-      <c r="D51" t="str">
-        <v>1-4</v>
-      </c>
-      <c r="E51" t="str">
-        <v>Trabajó bastante bien a dos manos y el legato de 5 notas. Trababó bastante bien los intervalos en la mano izquierda, ya que hacer los acordes presentan cierta dificultad.</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v/>
-      </c>
-      <c r="B52" t="str">
-        <v>Pequeños compañeros - Chwatal</v>
-      </c>
-      <c r="C52" t="str">
-        <v xml:space="preserve">Simultaneidad </v>
-      </c>
-      <c r="D52" t="str">
-        <v>1-8</v>
-      </c>
-      <c r="E52" t="str">
-        <v>Seguimos trabajando a dos manos y el legato de 5 notas. Trababó bastante bien los intervalos en la mano izquierda, ya que hacer los acordes presentan cierta dificultad.</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>Tomas</v>
-      </c>
-      <c r="B53" t="str">
-        <v>Pas Vite</v>
-      </c>
-      <c r="C53" t="str">
-        <v>Legato y Portato</v>
-      </c>
-      <c r="D53" t="str">
-        <v>1-4</v>
-      </c>
-      <c r="E53" t="str">
-        <v>Trabajó muy bien el uso del brazo, y el legato de tres notas., , Tocó la pieza de manera exitosa acompañado de su profesor. Debe hacer más ejercicios de fuerza o de brazo. (Cada dedo de manera separada con brazo)</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v/>
-      </c>
-      <c r="B54" t="str">
-        <v>Dance en do mayor - Gurlitt</v>
-      </c>
-      <c r="C54" t="str">
-        <v>Legato</v>
-      </c>
-      <c r="D54" t="str">
-        <v>1-8</v>
-      </c>
-      <c r="E54" t="str">
-        <v xml:space="preserve">Debemos seguir trabajando la mano izquierda por que le cuesta hacer 5to dedo., Estamos trabajando bien la correcta posición de los dedos al momento de hacer legatos. Está tocando bien de la tecla hacia abajo. , </v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v/>
-      </c>
-      <c r="B55" t="str">
-        <v>Danse de Lutins</v>
-      </c>
-      <c r="C55" t="str">
-        <v>Fraseo</v>
-      </c>
-      <c r="D55" t="str">
-        <v>1-8</v>
-      </c>
-      <c r="E55" t="str">
-        <v>Trabajó bien el motivo principal y su respectiva respuesta, ejecutó muy bien el legato de tres notas.</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v/>
-      </c>
-      <c r="B56" t="str">
-        <v>Danza Rusa</v>
-      </c>
-      <c r="C56" t="str">
-        <v>Legato</v>
-      </c>
-      <c r="D56" t="str">
-        <v>1-8</v>
-      </c>
-      <c r="E56" t="str">
         <v>Trabajó muy bien el Legato de tres notas acompañado de su profesor.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E42"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/estudiantes.xlsx
+++ b/estudiantes.xlsx
@@ -430,7 +430,7 @@
         <v>1-8</v>
       </c>
       <c r="E2" t="str">
-        <v xml:space="preserve">Ejecutó muy bien el Legato de 3 notas, haciendo buen uso del brazo(gesto de liberación)., Tocó la pieza acompañada de su profesor. </v>
+        <v xml:space="preserve">Repasó muy bien el Legato de 3 notas, haciendo buen uso del brazo(gesto de liberación)., Tocó la pieza acompañada de su profesor. </v>
       </c>
     </row>
     <row r="3">
@@ -447,7 +447,7 @@
         <v>1-4</v>
       </c>
       <c r="E3" t="str">
-        <v>Seguimos trabajando primer sistema con dos manos. Esta haciendo buen uso del 3er(Aunque este le cuesta un poco más) y 5to dedo en la mano izquierda.</v>
+        <v>Repasó trabajando primer sistema con dos manos. Esta haciendo buen uso del 3er(Aunque este le cuesta un poco más) y 5to dedo en la mano izquierda.</v>
       </c>
     </row>
     <row r="4">
@@ -503,7 +503,7 @@
         <v>1-8</v>
       </c>
       <c r="E7" t="str">
-        <v xml:space="preserve">Ha terminado el primer sistema pero debe trabajar mucho la anticipación para lograr una fluidez mínima deseada. La veo un poco  nerviosa al momento de grabar . Propongo que traté de tocar más para sus familiares y amigos cuando cuente con el tiempo. , , , </v>
+        <v xml:space="preserve">Ha terminado el primer período pero debe trabajar mucho la anticipación para lograr una fluidez mínima deseada. La veo un poco  nerviosa al momento de grabar . Propongo que traté de tocar más para sus familiares y amigos cuando cuente con el tiempo. , , , </v>
       </c>
     </row>
     <row r="8">
@@ -537,7 +537,7 @@
         <v>1-8</v>
       </c>
       <c r="E9" t="str">
-        <v xml:space="preserve">Repasamos segundo sistema, le cuesta los cambios tanto en la izquierda como la derecha(le confunde la melodía pero no por dificultad técnica, más bien por que no le parece tan intuitiva, debe escucharla con más atención),  es muy importante que practique más para conseguir tocar con más fluidez. Debe de concentrarse más en estudiar esa segunda parte </v>
+        <v xml:space="preserve">Repasamos segundo sistema, trabajó mejor los cambios tanto en la izquierda como la derecha, debe escuchar con más atención la melodía,  es muy importante que practique más para conseguir tocar con más fluidez. Debe de concentrarse más en estudiar esa segunda parte </v>
       </c>
     </row>
     <row r="10">
@@ -554,7 +554,7 @@
         <v>1-4</v>
       </c>
       <c r="E10" t="str">
-        <v>Terminó la pieza, debe esforzarse por recordar la posición de los dedos al empezar la pieza. Uso correcto uso de 5to dedo.</v>
+        <v>NO VINO, Terminó la pieza, debe esforzarse por recordar la posición de los dedos al empezar la pieza. Uso correcto uso de 5to dedo.</v>
       </c>
     </row>
     <row r="11">
@@ -588,7 +588,7 @@
         <v>1-8</v>
       </c>
       <c r="E12" t="str">
-        <v>Estudiamos  los dos primeros sistemas(Solo Mano Derecha). Haciendo énfasis en el uso de tercer y cuarto dedo(que se le dificulta un poco). Le causa gran estres tocar con la izquierda.</v>
+        <v>NO VINO, Estudiamos  los dos primeros sistemas(Solo Mano Derecha). Haciendo énfasis en el uso de tercer y cuarto dedo(que se le dificulta un poco). Le causa gran estres tocar con la izquierda.</v>
       </c>
     </row>
     <row r="13">
@@ -633,7 +633,7 @@
         <v>1-32</v>
       </c>
       <c r="E15" t="str">
-        <v xml:space="preserve">Terminamos la pieza, es necesario seguir trabajando la pieza concentrados en el tempo y cuidando la digitación., Continuamos trabajando haciendo énfasis en los acentos que debe hacer para no perder el ritmo de la pieza., Trabajó bastante bien a dos manos, hicimos énfasis en el tempo., , </v>
+        <v xml:space="preserve">NO VINO 1ro Mayo, Terminamos la pieza, es necesario seguir trabajando la pieza concentrados en el tempo y cuidando la digitación., Continuamos trabajando haciendo énfasis en los acentos que debe hacer para no perder el ritmo de la pieza., Trabajó bastante bien a dos manos, hicimos énfasis en el tempo., , </v>
       </c>
     </row>
     <row r="16">
@@ -695,7 +695,7 @@
         <v>1-8</v>
       </c>
       <c r="E19" t="str">
-        <v xml:space="preserve">Trabajamos toda la pieza, debe cuidar no esconder los dedos de la mano izquierda, en la izquierda solo va a hacer intervalos., , </v>
+        <v xml:space="preserve">NO VINO, Trabajamos toda la pieza, debe cuidar no esconder los dedos de la mano izquierda, en la izquierda solo va a hacer intervalos., , </v>
       </c>
     </row>
     <row r="20">
@@ -746,7 +746,7 @@
         <v>1-12</v>
       </c>
       <c r="E22" t="str">
-        <v xml:space="preserve">Ejecutó toda la pieza, pero le falta mas fluidez.  Debemos seguir repasando insistentemente por que  no tiene piano en su casa., </v>
+        <v xml:space="preserve">NO VINO, Ejecutó toda la pieza, pero le falta mas fluidez.  Debemos seguir repasando insistentemente por que  no tiene piano en su casa., </v>
       </c>
     </row>
     <row r="23">
@@ -780,7 +780,7 @@
         <v>1-8</v>
       </c>
       <c r="E24" t="str">
-        <v xml:space="preserve">No Vino, Terminó la primera y segunda parte , pero hay que repasar con constancia para que realmente suene fluido. Le cuesta un poco el cambio de acorde(tercer dedo de mano izquierda) pero lo está haciendo bastante bien., </v>
+        <v xml:space="preserve">, Terminó la primera y segunda parte , pero hay que repasar con constancia para que realmente suene fluido. Le cuesta un poco el cambio de acorde(tercer dedo de mano izquierda) pero lo está haciendo bastante bien., </v>
       </c>
     </row>
     <row r="25">
@@ -797,7 +797,7 @@
         <v>1-8</v>
       </c>
       <c r="E25" t="str">
-        <v>Trabajó muy bien con mano derecha e izquieda el motivo principal.Haciendo buen uso de brazo.</v>
+        <v>Trabajó muy bien con su profesor la alternancia de mano derecha e izquierda el motivo principal. Haciendo buen uso de brazo.</v>
       </c>
     </row>
     <row r="26">
@@ -865,7 +865,7 @@
         <v>1-16</v>
       </c>
       <c r="E29" t="str">
-        <v xml:space="preserve">Estamos trabajando tercer sistema con manos unidas. Ya se siente más cómodo con el ritmo. , , </v>
+        <v xml:space="preserve">Seguimos trabajando tercer sistema con manos unidas. Ya se siente más cómodo con el ritmo. , , </v>
       </c>
     </row>
     <row r="30">
@@ -882,7 +882,7 @@
         <v xml:space="preserve">1-8 </v>
       </c>
       <c r="E30" t="str">
-        <v xml:space="preserve">Trabajamos tercer sistema con manos unidas, solo estamos haciendo acordes en la izquierda. Ya terminó la pieza pero le falta practicar más el final. </v>
+        <v xml:space="preserve">Trabajamos toda la primera página con manos unidas, solo estamos haciendo acordes en la izquierda a partir del segundo sistema para hacerlo más fácil para él. Debe practicar más. </v>
       </c>
     </row>
     <row r="31" xml:space="preserve">
@@ -899,7 +899,7 @@
         <v>1-8</v>
       </c>
       <c r="E31" t="str" xml:space="preserve">
-        <v xml:space="preserve">
+        <v xml:space="preserve">NO VINO 1ro MAYO, , 
 Empezamos segunda parte y repasamos la primera parte, mostró interés por el ritmo.</v>
       </c>
     </row>
@@ -951,7 +951,7 @@
         <v>1-8</v>
       </c>
       <c r="E34" t="str">
-        <v xml:space="preserve">Repasamos hasta el segundo sistema con manos unidas. Se le está acompañando usando solfeo. Hay que repetirle insistentemente que cuide la posición de su cuerpo.  , </v>
+        <v xml:space="preserve">Seguimos repasando solo los dos primeros sistemas con manos unidas. Se le está acompañando usando solfeo. Hay que repetirle insistentemente que cuide la posición de su cuerpo.  , </v>
       </c>
     </row>
     <row r="35">
@@ -968,7 +968,7 @@
         <v xml:space="preserve">1-8 </v>
       </c>
       <c r="E35" t="str">
-        <v xml:space="preserve">Empezamos primer sistema a dos manos con relativa facilidad, debe tener cuidado en donde debe acompañar adecuadamente con la izquierda.  </v>
+        <v xml:space="preserve">Trabajamos una primera parte y se le envió video de el mismo tocando esa parte, debe tener cuidado en donde debe acompañar adecuadamente con la izquierda.  </v>
       </c>
     </row>
     <row r="36">
@@ -1002,7 +1002,7 @@
         <v>1-4</v>
       </c>
       <c r="E37" t="str">
-        <v>Trabajó bastante bien a dos manos y el legato de 5 notas. Trababó bastante bien los intervalos en la mano izquierda, ya que hacer los acordes presentan cierta dificultad.</v>
+        <v>Trabajó bastante bien a dos manos y el legato de 5 notas. Trabajó bastante bien los intervalos en la mano izquierda, ya que hacer los acordes presentan cierta dificultad.</v>
       </c>
     </row>
     <row r="38">
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="B38" t="str">
-        <v>Pequeños compañeros - Chwatal</v>
+        <v>Oompa Loompa - Leslie Bricusse and Anthony Newley</v>
       </c>
       <c r="C38" t="str">
         <v xml:space="preserve">Simultaneidad </v>
       </c>
       <c r="D38" t="str">
-        <v>1-8</v>
+        <v>1-12</v>
       </c>
       <c r="E38" t="str">
-        <v>Seguimos trabajando a dos manos y el legato de 5 notas. Trababó bastante bien los intervalos en la mano izquierda, ya que hacer los acordes presentan cierta dificultad.</v>
+        <v>Trabajó muy bien con su profesor el ritmo, le costó recordar al principio la melodía, debe seguir repasando y no confiarse.</v>
       </c>
     </row>
     <row r="39">
@@ -1036,7 +1036,7 @@
         <v>1-4</v>
       </c>
       <c r="E39" t="str">
-        <v>Trabajó muy bien el uso del brazo, y el legato de tres notas., , Tocó la pieza de manera exitosa acompañado de su profesor. Debe hacer más ejercicios de fuerza o de brazo. (Cada dedo de manera separada con brazo)</v>
+        <v>NO VINO, Trabajó muy bien el uso del brazo, y el legato de tres notas., , Tocó la pieza de manera exitosa acompañado de su profesor. Debe hacer más ejercicios de fuerza o de brazo. (Cada dedo de manera separada con brazo)</v>
       </c>
     </row>
     <row r="40">
